--- a/OMOP Analysis/Results/Cohort/Output_GT_overall_healthcare_roles-OMOP.xlsx
+++ b/OMOP Analysis/Results/Cohort/Output_GT_overall_healthcare_roles-OMOP.xlsx
@@ -357,7 +357,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>**Table of Healthcare Categories**</t>
+          <t>OMOP</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
